--- a/mobile/app/src/test/resources/backend_export.xlsx
+++ b/mobile/app/src/test/resources/backend_export.xlsx
@@ -11,6 +11,8 @@
     <sheet name="布点明细" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="采购记录" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="额外费用" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="分组" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="分类" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -416,149 +418,155 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S2"/>
+  <dimension ref="A1:U2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
+          <t>物料ID</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
           <t>类目</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>物料名称</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>品牌</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>型号</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>单位</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>数量</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>单价</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>优惠单价</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>日常价</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>实付数量</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>实付金额</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>未付数量</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>未付金额</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>日常价未付</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>实际优惠</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>日常价优惠</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>已购</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
-        <is>
-          <t>物料ID</t>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>添加时间</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>修改时间</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
         <is>
           <t>照明</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="C2" t="inlineStr">
         <is>
           <t>筒灯</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="D2" t="inlineStr">
         <is>
           <t>松下</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>NN-3021</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr">
         <is>
           <t>个</t>
         </is>
       </c>
-      <c r="F2" t="n">
+      <c r="G2" t="n">
         <v>6</v>
       </c>
-      <c r="G2" t="n">
+      <c r="H2" t="n">
         <v>30.5</v>
       </c>
-      <c r="I2" t="n">
+      <c r="J2" t="n">
         <v>183</v>
       </c>
-      <c r="J2" t="n">
+      <c r="K2" t="n">
         <v>6</v>
       </c>
-      <c r="K2" t="n">
+      <c r="L2" t="n">
         <v>180.5</v>
-      </c>
-      <c r="L2" t="n">
-        <v>0</v>
       </c>
       <c r="M2" t="n">
         <v>0</v>
@@ -567,19 +575,29 @@
         <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="P2" t="n">
         <v>2.5</v>
       </c>
-      <c r="Q2" t="inlineStr">
+      <c r="Q2" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="R2" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="R2" t="inlineStr"/>
-      <c r="S2" t="n">
-        <v>1</v>
+      <c r="S2" t="inlineStr"/>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>2026-10-07 17:49:41</t>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>2026-10-07 17:49:41</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -599,53 +617,53 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
+          <t>物料ID</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
           <t>物料名称</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>房间</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>数量</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>单价</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>物料ID</t>
-        </is>
-      </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
         <is>
           <t>筒灯</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="C2" t="inlineStr">
         <is>
           <t>客厅</t>
         </is>
       </c>
-      <c r="C2" t="n">
+      <c r="D2" t="n">
         <v>6</v>
       </c>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="n">
-        <v>1</v>
-      </c>
+      <c r="F2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -658,83 +676,111 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I2"/>
+  <dimension ref="A1:K2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
+          <t>物料ID</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
           <t>物料名称</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>实付数量</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>实付金额</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>付款日期</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>分组</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>商家</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>订单号</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>物料ID</t>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>添加时间</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>修改时间</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
         <is>
           <t>筒灯</t>
         </is>
       </c>
-      <c r="B2" t="n">
+      <c r="C2" t="n">
         <v>6</v>
       </c>
-      <c r="C2" t="n">
+      <c r="D2" t="n">
         <v>180.5</v>
       </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>2026-09-01</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr"/>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
       <c r="F2" t="inlineStr">
         <is>
+          <t>客厅</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
           <t>京东</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="n">
-        <v>1</v>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>JD20260914001</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>2026-10-07 17:49:41</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>2026-10-07 17:49:41</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -748,7 +794,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:H2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -782,6 +828,16 @@
           <t>备注</t>
         </is>
       </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>添加时间</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>修改时间</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -790,16 +846,90 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>80</v>
+        <v>120</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr"/>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>京东</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>JD20260914001</t>
+        </is>
+      </c>
       <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>2026-10-07 17:49:41</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>2026-10-07 17:49:41</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:A2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>分组名称</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>客厅</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:A2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>分类名称</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>照明</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/mobile/app/src/test/resources/backend_export.xlsx
+++ b/mobile/app/src/test/resources/backend_export.xlsx
@@ -591,12 +591,12 @@
       <c r="S2" t="inlineStr"/>
       <c r="T2" t="inlineStr">
         <is>
-          <t>2026-10-07 17:49:41</t>
+          <t>2026-10-08 15:53:16.718501+08:00</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>2026-10-07 17:49:41</t>
+          <t>2026-10-08 15:53:16.718503+08:00</t>
         </is>
       </c>
     </row>
@@ -774,12 +774,12 @@
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr">
         <is>
-          <t>2026-10-07 17:49:41</t>
+          <t>2026-10-08 15:53:16.719553+08:00</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>2026-10-07 17:49:41</t>
+          <t>2026-10-08 15:53:16.719555+08:00</t>
         </is>
       </c>
     </row>
@@ -866,12 +866,12 @@
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2026-10-07 17:49:41</t>
+          <t>2026-10-08 15:53:16.720155+08:00</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2026-10-07 17:49:41</t>
+          <t>2026-10-08 15:53:16.720157+08:00</t>
         </is>
       </c>
     </row>
